--- a/data_dictionary/cis9440-data_dictionary.xlsx
+++ b/data_dictionary/cis9440-data_dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rinas\Documents\Baruch College\Fall 2025 Semester\CIS 9440\Individual Assignment\cis9440_dwh_metrobike\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC4607E-B3D5-4D69-9759-CD12025B4D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2DAB08-2640-4CEB-A3FA-D0B62CC898E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{36F46622-3DD2-45A9-8E12-C6834B8F1A91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="125">
   <si>
     <t>Column Name</t>
   </si>
@@ -183,6 +183,234 @@
   </si>
   <si>
     <t>year</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Field Name</t>
+  </si>
+  <si>
+    <t>Source Column</t>
+  </si>
+  <si>
+    <t>Transformed?</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>staging_trips</t>
+  </si>
+  <si>
+    <t>BIGINT</t>
+  </si>
+  <si>
+    <t>Original trip identifier</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>Bike identifier</t>
+  </si>
+  <si>
+    <t>Raw datetime string</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>dim_date.full_date</t>
+  </si>
+  <si>
+    <t>Checkout time only</t>
+  </si>
+  <si>
+    <t>Kiosk where trip started</t>
+  </si>
+  <si>
+    <t>dim_kiosk</t>
+  </si>
+  <si>
+    <t>Kiosk where trip ended</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>fact_bike_trips</t>
+  </si>
+  <si>
+    <t>Unused</t>
+  </si>
+  <si>
+    <t>socrata_id</t>
+  </si>
+  <si>
+    <t>socrata_version</t>
+  </si>
+  <si>
+    <t>socrata_created_at</t>
+  </si>
+  <si>
+    <t>socrata_updated_at</t>
+  </si>
+  <si>
+    <t>dim_date</t>
+  </si>
+  <si>
+    <t>date_sk</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Generated</t>
+  </si>
+  <si>
+    <t>full_date</t>
+  </si>
+  <si>
+    <t>Extracted</t>
+  </si>
+  <si>
+    <t>quarter</t>
+  </si>
+  <si>
+    <t>Month number</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>Day of month</t>
+  </si>
+  <si>
+    <t>weekday</t>
+  </si>
+  <si>
+    <t>dim_bike</t>
+  </si>
+  <si>
+    <t>bike_sk</t>
+  </si>
+  <si>
+    <t>Bike type</t>
+  </si>
+  <si>
+    <t>dim_membership</t>
+  </si>
+  <si>
+    <t>membership_sk</t>
+  </si>
+  <si>
+    <t>Membership category</t>
+  </si>
+  <si>
+    <t>kiosk_sk</t>
+  </si>
+  <si>
+    <t>kiosk_id</t>
+  </si>
+  <si>
+    <t>Original kiosk ID</t>
+  </si>
+  <si>
+    <t>kiosk_name</t>
+  </si>
+  <si>
+    <t>Kiosk name</t>
+  </si>
+  <si>
+    <t>kiosk_location</t>
+  </si>
+  <si>
+    <t>trip_sk</t>
+  </si>
+  <si>
+    <t>Original trip ID</t>
+  </si>
+  <si>
+    <t>FK to dim_date</t>
+  </si>
+  <si>
+    <t>Join lookup</t>
+  </si>
+  <si>
+    <t>checkout_kiosk_sk</t>
+  </si>
+  <si>
+    <t>return_kiosk_sk</t>
+  </si>
+  <si>
+    <t>duration_minutes</t>
+  </si>
+  <si>
+    <t>Membership type</t>
+  </si>
+  <si>
+    <t>Bike type (Standard/Electric)</t>
+  </si>
+  <si>
+    <t>Checkout date</t>
+  </si>
+  <si>
+    <t>Trip duration</t>
+  </si>
+  <si>
+    <t>Month extracted by API</t>
+  </si>
+  <si>
+    <t>Year extracted by API</t>
+  </si>
+  <si>
+    <t>Metadata</t>
+  </si>
+  <si>
+    <t>Surrogate key</t>
+  </si>
+  <si>
+    <t>Full date</t>
+  </si>
+  <si>
+    <t>Cast</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Weekday name</t>
+  </si>
+  <si>
+    <t>Original bike ID</t>
+  </si>
+  <si>
+    <t>Distinct</t>
+  </si>
+  <si>
+    <t>checkout_kiosk_id / return_kiosk_id</t>
+  </si>
+  <si>
+    <t>checkout_kiosk / return_kiosk</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>FK kiosk</t>
+  </si>
+  <si>
+    <t>FK bike</t>
+  </si>
+  <si>
+    <t>FK membership</t>
   </si>
 </sst>
 </file>
@@ -212,7 +440,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -227,6 +455,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -255,12 +507,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
@@ -268,9 +524,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="7">
+    <cellStyle name="20% - Accent1" xfId="3" builtinId="30"/>
+    <cellStyle name="20% - Accent2" xfId="4" builtinId="34"/>
+    <cellStyle name="20% - Accent3" xfId="5" builtinId="38"/>
     <cellStyle name="20% - Accent4" xfId="2" builtinId="42"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -604,13 +868,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385FB75F-7879-44A2-A2FC-8056AD59B8BB}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="84.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -823,6 +1090,995 @@
         <v>48</v>
       </c>
     </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
